--- a/output/_temp/etapa_3_clasificacion/registros_clasificados.xlsx
+++ b/output/_temp/etapa_3_clasificacion/registros_clasificados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>MATRIZ_TERRENO</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>CODIGO_CIERRE</t>
         </is>
       </c>
@@ -472,11 +477,8 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/_temp/etapa_3_clasificacion/registros_clasificados.xlsx
+++ b/output/_temp/etapa_3_clasificacion/registros_clasificados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,41 +444,54 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>COMENTARIO_MENSUAL</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>DESC_TAREA_2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>GRUPO_TRAB</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>CODIGO</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ORIGEN_HOJA</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ORIGEN_FILA</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>MATRIZ_TERRENO</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>CODIGO_CIERRE</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>PZ-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AGUA</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
